--- a/excel/planilha_openpyxl.xlsx
+++ b/excel/planilha_openpyxl.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Clientes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +25,58 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FF8C00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+        <bgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00666666"/>
+        <bgColor rgb="00666666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f4ddcb"/>
+        <bgColor rgb="00f4ddcb"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -43,12 +84,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00000080"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00FF8C00"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,29 +479,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nome do Produto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Quantidade</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Preço</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Reservado</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>NOME DO PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>QUANTIDADE</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>PREÇO</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
     </row>
@@ -461,10 +522,8 @@
           <t>usado</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
+      <c r="E2" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -481,8 +540,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>novo</t>
-        </is>
+          <t>usado</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -502,6 +564,9 @@
           <t>novo</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -520,6 +585,9 @@
           <t>usado</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +606,9 @@
           <t>novo</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -556,6 +627,9 @@
           <t>novo</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -574,6 +648,9 @@
           <t>novo</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>7500</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -591,22 +668,12 @@
         <is>
           <t>usado</t>
         </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/excel/planilha_openpyxl.xlsx
+++ b/excel/planilha_openpyxl.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$E$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +43,32 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF6A00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00606060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00606060"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00606060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -76,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -99,17 +127,77 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00FF6A00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00f4ddcb"/>
+      </left>
+      <right style="thin">
+        <color rgb="00f4ddcb"/>
+      </right>
+      <top style="thin">
+        <color rgb="00f4ddcb"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00f4ddcb"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00FF6A00"/>
+      </left>
+      <right style="thick">
+        <color rgb="00FF6A00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00f4ddcb"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00f4ddcb"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,203 +565,211 @@
   </sheetPr>
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>NOME DO PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Toca-discos Pioneer</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="16" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>3 em Um Philips</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="16" t="n">
         <v>600</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="16" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>CD Pink Floyd Animals</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="16" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>LP Pink Floyd Pulse</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="16" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CD Pink Floyd The Wall</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="16" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CD Black Sabbath 13</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="16" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>BOX Black Sabbath 13</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="16" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Blueray Philips</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="16" t="n">
         <v>800</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="16" t="n">
         <v>1600</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel/planilha_openpyxl.xlsx
+++ b/excel/planilha_openpyxl.xlsx
@@ -104,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -160,11 +160,39 @@
         <color rgb="00f4ddcb"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FF6A00"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FF6A00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00f4ddcb"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00f4ddcb"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FF6A00"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FF6A00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00f4ddcb"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FF6A00"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +224,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,205 +603,205 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>NOME DO PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Toca-discos Pioneer</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="18" t="n">
         <v>500</v>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="18" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>3 em Um Philips</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="18" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>CD Pink Floyd Animals</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="18" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>LP Pink Floyd Pulse</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="18" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>CD Pink Floyd The Wall</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="18" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>CD Black Sabbath 13</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="18" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>BOX Black Sabbath 13</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>novo</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="18" t="n">
         <v>7500</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Blueray Philips</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="19" t="n">
         <v>800</v>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>usado</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="19" t="n">
         <v>1600</v>
       </c>
     </row>

--- a/excel/planilha_openpyxl.xlsx
+++ b/excel/planilha_openpyxl.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
       <name val="Arial"/>
       <color rgb="00333333"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF6A00"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -192,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,6 +239,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -309,6 +318,20 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaProdutos" displayName="TabelaProdutos" ref="A1:E9" headerRowCount="1">
+  <autoFilter ref="A1:E9"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="NOME DO PRODUTO"/>
+    <tableColumn id="2" name="QUANTIDADE"/>
+    <tableColumn id="3" name="PREÇO"/>
+    <tableColumn id="4" name="ESTADO"/>
+    <tableColumn id="5" name="TOTAL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,27 +634,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>NOME DO PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -808,5 +831,8 @@
   </sheetData>
   <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>